--- a/src/test/resources/TestDriver/Hearst/ActivityData/CDB_BILL_20260831.xlsx
+++ b/src/test/resources/TestDriver/Hearst/ActivityData/CDB_BILL_20260831.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b68cc7b829e61597/Desktop/Hearst_Project/Sandbox/FileBreakup/CDB_BILL_by_postingdate/CDB_BILL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\fyntrac-data\src\test\resources\TestDriver\Hearst\ActivityData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_64AB98CCD34F90CEE941C4F45B5DCE3AA7C728E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{026215B0-DE63-4531-906B-4DF468412EB6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57066125-0B02-429D-BB8C-8B1222948AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12387" uniqueCount="3531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12423" uniqueCount="3544">
   <si>
     <t>PostingDate</t>
   </si>
@@ -10629,6 +10629,45 @@
   </si>
   <si>
     <t>1832474</t>
+  </si>
+  <si>
+    <t>Azz5ZXVGJEHlIHOf-1280587</t>
+  </si>
+  <si>
+    <t>-mm8d0btJu2</t>
+  </si>
+  <si>
+    <t>AYhSPNQIO4V</t>
+  </si>
+  <si>
+    <t>li_16BT9OVTX59Rt9bjs</t>
+  </si>
+  <si>
+    <t>AzZMiqVNHbYrI1ROC-1541337</t>
+  </si>
+  <si>
+    <t>RtzmgciUdb2</t>
+  </si>
+  <si>
+    <t>XjbG1utb_9D</t>
+  </si>
+  <si>
+    <t>li_16A0DwVSYVCNA3lpH</t>
+  </si>
+  <si>
+    <t>CREDITNOTE</t>
+  </si>
+  <si>
+    <t>CN-211770</t>
+  </si>
+  <si>
+    <t>1280587</t>
+  </si>
+  <si>
+    <t>CN-199245</t>
+  </si>
+  <si>
+    <t>1541337</t>
   </si>
 </sst>
 </file>
@@ -10981,7 +11020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2064"/>
+  <dimension ref="A1:I2070"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" customWidth="1"/>
@@ -70851,6 +70890,180 @@
         <v>696</v>
       </c>
     </row>
+    <row r="2065" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2065" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B2065" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2065" t="s">
+        <v>3531</v>
+      </c>
+      <c r="D2065" t="s">
+        <v>3532</v>
+      </c>
+      <c r="E2065" t="s">
+        <v>3539</v>
+      </c>
+      <c r="F2065" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2065">
+        <v>0</v>
+      </c>
+      <c r="H2065" t="s">
+        <v>3540</v>
+      </c>
+      <c r="I2065" t="s">
+        <v>3541</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2066" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B2066" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2066" t="s">
+        <v>3531</v>
+      </c>
+      <c r="D2066" t="s">
+        <v>3533</v>
+      </c>
+      <c r="E2066" t="s">
+        <v>3539</v>
+      </c>
+      <c r="F2066" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2066">
+        <v>0</v>
+      </c>
+      <c r="H2066" t="s">
+        <v>3540</v>
+      </c>
+      <c r="I2066" t="s">
+        <v>3541</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2067" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B2067" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C2067" t="s">
+        <v>3531</v>
+      </c>
+      <c r="D2067" t="s">
+        <v>3534</v>
+      </c>
+      <c r="E2067" t="s">
+        <v>3539</v>
+      </c>
+      <c r="F2067" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2067">
+        <v>-9.1999999999999993</v>
+      </c>
+      <c r="H2067" t="s">
+        <v>3540</v>
+      </c>
+      <c r="I2067" t="s">
+        <v>3541</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2068" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B2068" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C2068" t="s">
+        <v>3535</v>
+      </c>
+      <c r="D2068" t="s">
+        <v>3536</v>
+      </c>
+      <c r="E2068" t="s">
+        <v>3539</v>
+      </c>
+      <c r="F2068" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2068">
+        <v>0</v>
+      </c>
+      <c r="H2068" t="s">
+        <v>3542</v>
+      </c>
+      <c r="I2068" t="s">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2069" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B2069" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C2069" t="s">
+        <v>3535</v>
+      </c>
+      <c r="D2069" t="s">
+        <v>3537</v>
+      </c>
+      <c r="E2069" t="s">
+        <v>3539</v>
+      </c>
+      <c r="F2069" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2069">
+        <v>0</v>
+      </c>
+      <c r="H2069" t="s">
+        <v>3542</v>
+      </c>
+      <c r="I2069" t="s">
+        <v>3543</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2070" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B2070" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C2070" t="s">
+        <v>3535</v>
+      </c>
+      <c r="D2070" t="s">
+        <v>3538</v>
+      </c>
+      <c r="E2070" t="s">
+        <v>3539</v>
+      </c>
+      <c r="F2070" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2070">
+        <v>-14.99</v>
+      </c>
+      <c r="H2070" t="s">
+        <v>3542</v>
+      </c>
+      <c r="I2070" t="s">
+        <v>3543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
